--- a/data/trans_camb/P71_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P71_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 12,46</t>
+          <t>3,6; 12,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 9,87</t>
+          <t>1,73; 9,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,95</t>
+          <t>-5,16; 0,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 7,11</t>
+          <t>-4,29; 7,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 4,73</t>
+          <t>-5,19; 4,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -5,86</t>
+          <t>-13,99; -5,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 9,03</t>
+          <t>1,99; 8,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 6,59</t>
+          <t>0,39; 6,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,6; -2,73</t>
+          <t>-7,9; -2,82</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,53; 247,73</t>
+          <t>43,56; 251,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,33; 182,97</t>
+          <t>15,02; 195,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,36; 22,51</t>
+          <t>-59,83; 23,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 63,52</t>
+          <t>-28,41; 67,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,28; 46,64</t>
+          <t>-32,52; 49,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,12; -56,68</t>
+          <t>-85,15; -56,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,74; 114,49</t>
+          <t>17,6; 115,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 82,33</t>
+          <t>3,67; 79,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,58; -34,35</t>
+          <t>-69,46; -34,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 6,29</t>
+          <t>-4,22; 5,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 15,53</t>
+          <t>4,06; 15,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,06; -4,96</t>
+          <t>-13,18; -5,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 4,23</t>
+          <t>-7,78; 4,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 12,63</t>
+          <t>0,05; 13,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,57; -8,48</t>
+          <t>-17,97; -7,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 3,26</t>
+          <t>-4,53; 3,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 11,97</t>
+          <t>3,34; 11,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,2; -7,81</t>
+          <t>-14,07; -7,83</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 62,31</t>
+          <t>-28,76; 57,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,28; 152,12</t>
+          <t>23,92; 155,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-82,77; -49,01</t>
+          <t>-83,96; -46,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 24,84</t>
+          <t>-35,86; 26,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 78,48</t>
+          <t>-0,18; 82,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,12; -50,41</t>
+          <t>-77,38; -48,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 22,71</t>
+          <t>-25,05; 22,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,02; 86,14</t>
+          <t>18,59; 85,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,25; -56,73</t>
+          <t>-77,53; -54,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,81; 24,25</t>
+          <t>14,43; 24,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,3; 27,07</t>
+          <t>17,05; 27,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,66; -0,73</t>
+          <t>-14,02; -0,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 15,17</t>
+          <t>-1,21; 15,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 21,54</t>
+          <t>2,23; 21,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,54; -2,85</t>
+          <t>-17,09; -2,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,53; 20,0</t>
+          <t>11,64; 20,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,36; 25,11</t>
+          <t>14,77; 24,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,94; -2,2</t>
+          <t>-14,42; -2,63</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77,18; 186,43</t>
+          <t>78,45; 192,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92,41; 208,6</t>
+          <t>95,74; 214,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,16; -5,48</t>
+          <t>-79,21; -3,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 89,63</t>
+          <t>-5,05; 93,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 133,33</t>
+          <t>8,5; 126,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,42; -16,94</t>
+          <t>-65,67; -12,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,74; 138,24</t>
+          <t>61,55; 138,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84,6; 176,1</t>
+          <t>76,92; 166,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,96; -14,53</t>
+          <t>-78,58; -16,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,99; 19,43</t>
+          <t>11,82; 19,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,34; 20,11</t>
+          <t>11,94; 19,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,84; -3,79</t>
+          <t>-10,56; -3,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,06; 15,64</t>
+          <t>5,75; 15,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,35; 18,05</t>
+          <t>8,08; 17,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,83; -8,3</t>
+          <t>-20,7; -8,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,14; 17,08</t>
+          <t>10,8; 17,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,96; 17,86</t>
+          <t>12,11; 17,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,93; -6,92</t>
+          <t>-14,44; -6,79</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>49,21; 92,94</t>
+          <t>48,08; 94,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50,48; 94,86</t>
+          <t>48,31; 93,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-44,11; -17,97</t>
+          <t>-44,41; -18,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,92; 67,54</t>
+          <t>20,17; 68,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,63; 79,96</t>
+          <t>29,17; 77,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,47; -34,5</t>
+          <t>-73,01; -34,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,34; 77,62</t>
+          <t>43,22; 76,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>47,34; 80,29</t>
+          <t>48,85; 81,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,9; -30,93</t>
+          <t>-59,42; -30,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 14,16</t>
+          <t>0,55; 13,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,67; 19,96</t>
+          <t>6,86; 20,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,79; -2,73</t>
+          <t>-15,49; -2,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 11,68</t>
+          <t>0,57; 11,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,52; 23,68</t>
+          <t>12,26; 23,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 16,94</t>
+          <t>-8,25; 18,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 10,48</t>
+          <t>2,07; 10,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,2; 20,2</t>
+          <t>11,84; 20,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 9,77</t>
+          <t>-9,05; 8,14</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2,66; 47,26</t>
+          <t>1,22; 45,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17,27; 66,98</t>
+          <t>19,14; 69,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,79; -8,28</t>
+          <t>-41,42; -7,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,97; 37,11</t>
+          <t>1,56; 37,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>32,6; 73,24</t>
+          <t>31,48; 71,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 49,29</t>
+          <t>-22,82; 52,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,55; 32,34</t>
+          <t>5,46; 32,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>29,78; 63,66</t>
+          <t>31,53; 61,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 29,88</t>
+          <t>-25,04; 25,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,45; 15,12</t>
+          <t>2,65; 14,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,53; 17,44</t>
+          <t>4,68; 16,95</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 10,55</t>
+          <t>-5,21; 11,38</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 2,84</t>
+          <t>-4,52; 2,92</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 4,44</t>
+          <t>-3,69; 4,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,43; -11,29</t>
+          <t>-18,82; -11,35</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 3,94</t>
+          <t>-2,76; 4,29</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 5,59</t>
+          <t>-1,31; 5,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,76; -8,5</t>
+          <t>-15,51; -8,36</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15,78; 164,51</t>
+          <t>17,25; 161,76</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>30,91; 193,3</t>
+          <t>31,27; 184,12</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 108,96</t>
+          <t>-41,25; 130,04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 9,44</t>
+          <t>-13,32; 9,56</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 14,42</t>
+          <t>-10,43; 14,73</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,41; -36,29</t>
+          <t>-55,32; -36,48</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 14,97</t>
+          <t>-9,25; 15,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 20,91</t>
+          <t>-4,37; 19,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-52,1; -30,97</t>
+          <t>-51,73; -30,45</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10,25; 14,79</t>
+          <t>10,34; 14,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>13,33; 17,65</t>
+          <t>13,17; 17,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,97; -4,1</t>
+          <t>-9,32; -4,27</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,94</t>
+          <t>1,57; 5,92</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,25</t>
+          <t>5,75; 10,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,38; -5,75</t>
+          <t>-14,08; -5,36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,51</t>
+          <t>6,52; 9,59</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>10,13; 13,32</t>
+          <t>10,08; 13,14</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-10,65; -5,05</t>
+          <t>-10,71; -5,75</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>54,68; 86,39</t>
+          <t>54,22; 85,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>69,1; 103,29</t>
+          <t>68,63; 101,35</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-48,3; -23,56</t>
+          <t>-49,44; -24,32</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,79; 22,03</t>
+          <t>5,58; 22,1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,15; 38,28</t>
+          <t>20,02; 38,21</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-50,21; -20,28</t>
+          <t>-50,21; -19,27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,37; 43,11</t>
+          <t>27,48; 42,91</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>42,32; 60,27</t>
+          <t>42,17; 59,14</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-45,52; -21,83</t>
+          <t>-45,5; -24,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P71_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P71_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-10,0</t>
+          <t>-9,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,2</t>
+          <t>-4,81</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 12,5</t>
+          <t>4,06; 12,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 9,93</t>
+          <t>1,66; 9,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,99</t>
+          <t>-4,36; 2,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 7,28</t>
+          <t>-4,93; 6,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 4,82</t>
+          <t>-5,28; 5,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,99; -5,94</t>
+          <t>-14,17; -5,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,95</t>
+          <t>1,88; 8,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,4</t>
+          <t>0,35; 6,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,9; -2,82</t>
+          <t>-7,35; -2,31</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-28,27%</t>
+          <t>-22,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-74,7%</t>
+          <t>-71,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-55,54%</t>
+          <t>-51,37%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,56; 251,14</t>
+          <t>46,33; 248,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,02; 195,58</t>
+          <t>19,23; 190,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,83; 23,57</t>
+          <t>-54,06; 46,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 67,3</t>
+          <t>-30,29; 61,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 49,0</t>
+          <t>-33,05; 58,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,15; -56,53</t>
+          <t>-82,85; -54,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,6; 115,42</t>
+          <t>16,99; 113,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 79,97</t>
+          <t>2,16; 86,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,46; -34,08</t>
+          <t>-67,08; -29,88</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-8,8</t>
+          <t>-8,85</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,9</t>
+          <t>-12,69</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-10,99</t>
+          <t>-10,9</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 5,99</t>
+          <t>-3,87; 6,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 15,81</t>
+          <t>4,26; 15,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,18; -5,09</t>
+          <t>-12,87; -5,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 4,13</t>
+          <t>-7,99; 3,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 13,04</t>
+          <t>-0,24; 11,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,97; -7,85</t>
+          <t>-17,67; -8,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 3,15</t>
+          <t>-4,73; 3,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 11,82</t>
+          <t>3,77; 12,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,07; -7,83</t>
+          <t>-14,08; -7,83</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-70,05%</t>
+          <t>-70,44%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-66,45%</t>
+          <t>-65,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-68,64%</t>
+          <t>-68,07%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 57,93</t>
+          <t>-26,27; 60,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,92; 155,07</t>
+          <t>27,07; 156,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-83,96; -46,74</t>
+          <t>-83,89; -47,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 26,29</t>
+          <t>-36,59; 23,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 82,57</t>
+          <t>-1,26; 74,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-77,38; -48,99</t>
+          <t>-76,38; -48,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 22,76</t>
+          <t>-26,5; 24,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,59; 85,25</t>
+          <t>20,21; 84,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,53; -54,97</t>
+          <t>-77,09; -56,62</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,68</t>
+          <t>-1,57</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,65</t>
+          <t>-9,32</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,51</t>
+          <t>-3,47</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,43; 24,1</t>
+          <t>13,89; 23,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,05; 27,29</t>
+          <t>17,12; 27,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,02; -0,5</t>
+          <t>-6,11; 3,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 15,72</t>
+          <t>-1,83; 16,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 21,33</t>
+          <t>1,68; 21,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,09; -2,02</t>
+          <t>-16,61; -1,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,64; 20,05</t>
+          <t>11,43; 20,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,77; 24,59</t>
+          <t>15,27; 24,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -2,63</t>
+          <t>-7,18; 0,23</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-44,47%</t>
+          <t>-10,43%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-45,25%</t>
+          <t>-43,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-45,46%</t>
+          <t>-20,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78,45; 192,08</t>
+          <t>80,54; 187,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95,74; 214,49</t>
+          <t>99,7; 216,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,21; -3,77</t>
+          <t>-35,3; 24,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 93,68</t>
+          <t>-6,84; 102,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,5; 126,53</t>
+          <t>6,83; 131,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,67; -12,14</t>
+          <t>-63,37; -9,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,55; 138,91</t>
+          <t>59,55; 137,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>76,92; 166,66</t>
+          <t>81,91; 165,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,58; -16,79</t>
+          <t>-38,72; 1,85</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,3</t>
+          <t>-6,95</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-13,21</t>
+          <t>-9,06</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,79</t>
+          <t>-7,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,82; 19,5</t>
+          <t>11,97; 19,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,94; 19,67</t>
+          <t>12,42; 19,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -3,8</t>
+          <t>-10,49; -3,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,75; 15,83</t>
+          <t>5,97; 16,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,08; 17,59</t>
+          <t>7,87; 17,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,7; -8,64</t>
+          <t>-12,85; -4,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,8; 17,04</t>
+          <t>10,58; 17,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,11; 17,93</t>
+          <t>11,77; 17,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,44; -6,79</t>
+          <t>-10,33; -5,18</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-32,41%</t>
+          <t>-30,84%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-51,59%</t>
+          <t>-35,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-41,42%</t>
+          <t>-32,33%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>48,08; 94,19</t>
+          <t>49,03; 92,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,31; 93,56</t>
+          <t>51,87; 98,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-44,41; -18,11</t>
+          <t>-43,54; -17,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,17; 68,53</t>
+          <t>21,07; 69,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,17; 77,47</t>
+          <t>28,26; 76,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,01; -34,77</t>
+          <t>-45,82; -21,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,22; 76,85</t>
+          <t>41,42; 76,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>48,85; 81,75</t>
+          <t>46,85; 79,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,42; -30,62</t>
+          <t>-41,17; -22,76</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-9,23</t>
+          <t>-4,56</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-5,64</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,69</t>
+          <t>-5,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 13,91</t>
+          <t>0,99; 14,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,86; 20,18</t>
+          <t>6,91; 20,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -2,14</t>
+          <t>-10,95; 2,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 11,89</t>
+          <t>0,8; 11,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,26; 23,15</t>
+          <t>12,44; 23,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 18,04</t>
+          <t>-10,82; -0,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 10,63</t>
+          <t>2,02; 10,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,84; 20,01</t>
+          <t>11,51; 20,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 8,14</t>
+          <t>-9,7; -1,43</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-27,24%</t>
+          <t>-13,46%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-1,39%</t>
+          <t>-15,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-10,59%</t>
+          <t>-15,03%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,22; 45,48</t>
+          <t>2,68; 49,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19,14; 69,84</t>
+          <t>17,5; 67,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,42; -7,53</t>
+          <t>-28,69; 7,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,56; 37,04</t>
+          <t>1,96; 36,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>31,48; 71,58</t>
+          <t>31,47; 72,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 52,39</t>
+          <t>-27,73; -2,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,46; 32,54</t>
+          <t>5,29; 33,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>31,53; 61,79</t>
+          <t>31,12; 63,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 25,4</t>
+          <t>-25,57; -4,41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>4,25</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-15,15</t>
+          <t>-14,59</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-12,02</t>
+          <t>-11,01</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,65; 14,43</t>
+          <t>2,32; 15,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,68; 16,95</t>
+          <t>5,11; 17,87</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 11,38</t>
+          <t>-3,76; 14,03</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 2,92</t>
+          <t>-4,93; 2,88</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 4,55</t>
+          <t>-3,54; 4,32</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,82; -11,35</t>
+          <t>-18,53; -10,65</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 4,29</t>
+          <t>-2,52; 4,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 5,24</t>
+          <t>-0,96; 5,85</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,51; -8,36</t>
+          <t>-14,23; -7,2</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-46,5%</t>
+          <t>-44,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-42,09%</t>
+          <t>-38,54%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17,25; 161,76</t>
+          <t>14,57; 165,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31,27; 184,12</t>
+          <t>36,34; 199,83</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-41,25; 130,04</t>
+          <t>-27,46; 146,81</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 9,56</t>
+          <t>-14,2; 9,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 14,73</t>
+          <t>-10,24; 13,96</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-55,32; -36,48</t>
+          <t>-53,75; -34,25</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 15,56</t>
+          <t>-8,38; 15,49</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 19,59</t>
+          <t>-3,49; 21,53</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-51,73; -30,45</t>
+          <t>-48,12; -26,34</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-6,17</t>
+          <t>-3,91</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-11,03</t>
+          <t>-11,02</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-8,6</t>
+          <t>-7,49</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10,34; 14,64</t>
+          <t>10,35; 14,51</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>13,17; 17,53</t>
+          <t>13,41; 17,59</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,32; -4,27</t>
+          <t>-5,73; -1,88</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,92</t>
+          <t>1,42; 5,92</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,75; 10,14</t>
+          <t>5,71; 10,38</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,08; -5,36</t>
+          <t>-12,95; -9,23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,52; 9,59</t>
+          <t>6,23; 9,66</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>10,08; 13,14</t>
+          <t>9,98; 13,23</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-10,71; -5,75</t>
+          <t>-8,85; -6,2</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-34,04%</t>
+          <t>-21,58%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-39,62%</t>
+          <t>-39,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-37,32%</t>
+          <t>-32,52%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>54,22; 85,8</t>
+          <t>54,45; 84,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>68,63; 101,35</t>
+          <t>70,27; 103,27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-49,44; -24,32</t>
+          <t>-30,44; -11,13</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5,58; 22,1</t>
+          <t>5,0; 22,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,02; 38,21</t>
+          <t>19,71; 38,83</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-50,21; -19,27</t>
+          <t>-44,8; -34,52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,48; 42,91</t>
+          <t>26,26; 43,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>42,17; 59,14</t>
+          <t>41,39; 59,46</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-45,5; -24,45</t>
+          <t>-37,16; -27,39</t>
         </is>
       </c>
     </row>
